--- a/routes_output.xlsx
+++ b/routes_output.xlsx
@@ -580,28 +580,28 @@
         <v>30</v>
       </c>
       <c r="M2" t="str">
-        <v>1830</v>
+        <v>0</v>
       </c>
       <c r="N2" t="str">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="O2" t="str">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="P2" t="str">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="str">
-        <v>$2,768</v>
+        <v>$0</v>
       </c>
       <c r="R2" t="str">
-        <v>$3,682</v>
+        <v>$0</v>
       </c>
       <c r="S2" t="str">
-        <v>$6,366</v>
+        <v>$0</v>
       </c>
       <c r="T2" t="str">
-        <v>$4,795</v>
+        <v>$0</v>
       </c>
       <c r="U2" t="str">
         <v>2191</v>
@@ -723,28 +723,28 @@
         <v>24</v>
       </c>
       <c r="M3" t="str">
-        <v>1396</v>
+        <v>0</v>
       </c>
       <c r="N3" t="str">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="O3" t="str">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="P3" t="str">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="str">
-        <v>$2,356</v>
+        <v>$0</v>
       </c>
       <c r="R3" t="str">
-        <v>$3,133</v>
+        <v>$0</v>
       </c>
       <c r="S3" t="str">
-        <v>$5,418</v>
+        <v>$0</v>
       </c>
       <c r="T3" t="str">
-        <v>$4,002</v>
+        <v>$0</v>
       </c>
       <c r="U3" t="str">
         <v>1516</v>
@@ -866,28 +866,28 @@
         <v>27</v>
       </c>
       <c r="M4" t="str">
-        <v>1846</v>
+        <v>0</v>
       </c>
       <c r="N4" t="str">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="O4" t="str">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P4" t="str">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="str">
-        <v>$2,735</v>
+        <v>$0</v>
       </c>
       <c r="R4" t="str">
-        <v>$3,637</v>
+        <v>$0</v>
       </c>
       <c r="S4" t="str">
-        <v>$6,289</v>
+        <v>$0</v>
       </c>
       <c r="T4" t="str">
-        <v>$4,736</v>
+        <v>$0</v>
       </c>
       <c r="U4" t="str">
         <v>1945</v>
@@ -1009,28 +1009,28 @@
         <v>25</v>
       </c>
       <c r="M5" t="str">
-        <v>764</v>
+        <v>0</v>
       </c>
       <c r="N5" t="str">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="O5" t="str">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="P5" t="str">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="str">
-        <v>$2,825</v>
+        <v>$0</v>
       </c>
       <c r="R5" t="str">
-        <v>$3,757</v>
+        <v>$0</v>
       </c>
       <c r="S5" t="str">
-        <v>$6,497</v>
+        <v>$0</v>
       </c>
       <c r="T5" t="str">
-        <v>$4,800</v>
+        <v>$0</v>
       </c>
       <c r="U5" t="str">
         <v>1834</v>
@@ -1295,16 +1295,16 @@
         <v>21</v>
       </c>
       <c r="M7" t="str">
-        <v>1434</v>
+        <v>600</v>
       </c>
       <c r="N7" t="str">
-        <v>254</v>
+        <v>52</v>
       </c>
       <c r="O7" t="str">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="P7" t="str">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="str">
         <v>$2,668</v>
@@ -1316,7 +1316,7 @@
         <v>$6,135</v>
       </c>
       <c r="T7" t="str">
-        <v>$4,620</v>
+        <v>$0</v>
       </c>
       <c r="U7" t="str">
         <v>1492</v>
@@ -1581,13 +1581,13 @@
         <v>30</v>
       </c>
       <c r="M9" t="str">
-        <v>912</v>
+        <v>420</v>
       </c>
       <c r="N9" t="str">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="O9" t="str">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="P9" t="str">
         <v>0</v>
@@ -2582,16 +2582,16 @@
         <v>29</v>
       </c>
       <c r="M16" t="str">
-        <v>1666</v>
+        <v>1010</v>
       </c>
       <c r="N16" t="str">
-        <v>396</v>
+        <v>106</v>
       </c>
       <c r="O16" t="str">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="P16" t="str">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="str">
         <v>$1,981</v>
@@ -2603,7 +2603,7 @@
         <v>$4,556</v>
       </c>
       <c r="T16" t="str">
-        <v>$3,429</v>
+        <v>$0</v>
       </c>
       <c r="U16" t="str">
         <v>1758</v>
@@ -2725,28 +2725,28 @@
         <v>29</v>
       </c>
       <c r="M17" t="str">
-        <v>656</v>
+        <v>0</v>
       </c>
       <c r="N17" t="str">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="O17" t="str">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="P17" t="str">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="str">
-        <v>$1,901</v>
+        <v>$0</v>
       </c>
       <c r="R17" t="str">
-        <v>$2,528</v>
+        <v>$0</v>
       </c>
       <c r="S17" t="str">
-        <v>$4,372</v>
+        <v>$0</v>
       </c>
       <c r="T17" t="str">
-        <v>$3,290</v>
+        <v>$0</v>
       </c>
       <c r="U17" t="str">
         <v>1762</v>
@@ -2868,28 +2868,28 @@
         <v>22</v>
       </c>
       <c r="M18" t="str">
-        <v>1949</v>
+        <v>0</v>
       </c>
       <c r="N18" t="str">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="O18" t="str">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P18" t="str">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="str">
-        <v>$2,609</v>
+        <v>$0</v>
       </c>
       <c r="R18" t="str">
-        <v>$3,470</v>
+        <v>$0</v>
       </c>
       <c r="S18" t="str">
-        <v>$6,001</v>
+        <v>$0</v>
       </c>
       <c r="T18" t="str">
-        <v>$4,519</v>
+        <v>$0</v>
       </c>
       <c r="U18" t="str">
         <v>1949</v>
@@ -3011,16 +3011,16 @@
         <v>25</v>
       </c>
       <c r="M19" t="str">
-        <v>1558</v>
+        <v>846</v>
       </c>
       <c r="N19" t="str">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="O19" t="str">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="P19" t="str">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="str">
         <v>$2,590</v>
@@ -3032,7 +3032,7 @@
         <v>$5,955</v>
       </c>
       <c r="T19" t="str">
-        <v>$4,484</v>
+        <v>$0</v>
       </c>
       <c r="U19" t="str">
         <v>1586</v>
@@ -3127,7 +3127,7 @@
         <v>9,487 km</v>
       </c>
       <c r="D20" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="str">
         <v>$15,456</v>
@@ -3136,10 +3136,10 @@
         <v>10</v>
       </c>
       <c r="G20" t="str">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H20" t="str">
-        <v>747-400 (GRU-MXP 2), A380-800 (GRU-0-4)</v>
+        <v>A380-800 (GRU-0-4)</v>
       </c>
       <c r="I20" t="str">
         <v>1957</v>
@@ -3190,13 +3190,13 @@
         <v>27</v>
       </c>
       <c r="Y20" t="str">
-        <v>1957</v>
+        <v>842</v>
       </c>
       <c r="Z20" t="str">
-        <v>340</v>
+        <v>274</v>
       </c>
       <c r="AA20" t="str">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="AB20" t="str">
         <v>27</v>
@@ -3220,7 +3220,7 @@
         <v>MXP</v>
       </c>
       <c r="AI20" t="str">
-        <v>747-400/GRU-MXP 2,A380-800/GRU-0-4</v>
+        <v>A380-800/GRU-0-4</v>
       </c>
       <c r="AJ20">
         <v>1957</v>
@@ -3235,13 +3235,13 @@
         <v>27</v>
       </c>
       <c r="AN20">
-        <v>1957</v>
+        <v>842</v>
       </c>
       <c r="AO20">
-        <v>340</v>
+        <v>274</v>
       </c>
       <c r="AP20">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="AQ20">
         <v>27</v>
@@ -3297,13 +3297,13 @@
         <v>23</v>
       </c>
       <c r="M21" t="str">
-        <v>2506</v>
+        <v>1422</v>
       </c>
       <c r="N21" t="str">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O21" t="str">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P21" t="str">
         <v>18</v>
@@ -3440,28 +3440,28 @@
         <v>23</v>
       </c>
       <c r="M22" t="str">
-        <v>1636</v>
+        <v>0</v>
       </c>
       <c r="N22" t="str">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="O22" t="str">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="P22" t="str">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="str">
-        <v>$2,382</v>
+        <v>$0</v>
       </c>
       <c r="R22" t="str">
-        <v>$3,168</v>
+        <v>$0</v>
       </c>
       <c r="S22" t="str">
-        <v>$5,478</v>
+        <v>$0</v>
       </c>
       <c r="T22" t="str">
-        <v>$4,046</v>
+        <v>$0</v>
       </c>
       <c r="U22" t="str">
         <v>1888</v>
@@ -3583,28 +3583,28 @@
         <v>25</v>
       </c>
       <c r="M23" t="str">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="N23" t="str">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="O23" t="str">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P23" t="str">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="str">
-        <v>$2,758</v>
+        <v>$0</v>
       </c>
       <c r="R23" t="str">
-        <v>$3,667</v>
+        <v>$0</v>
       </c>
       <c r="S23" t="str">
-        <v>$6,341</v>
+        <v>$0</v>
       </c>
       <c r="T23" t="str">
-        <v>$4,776</v>
+        <v>$0</v>
       </c>
       <c r="U23" t="str">
         <v>1846</v>
@@ -3726,28 +3726,28 @@
         <v>23</v>
       </c>
       <c r="M24" t="str">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="N24" t="str">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="O24" t="str">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="P24" t="str">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="str">
-        <v>$2,287</v>
+        <v>$0</v>
       </c>
       <c r="R24" t="str">
-        <v>$3,042</v>
+        <v>$0</v>
       </c>
       <c r="S24" t="str">
-        <v>$5,260</v>
+        <v>$0</v>
       </c>
       <c r="T24" t="str">
-        <v>$3,954</v>
+        <v>$0</v>
       </c>
       <c r="U24" t="str">
         <v>1596</v>
@@ -3842,7 +3842,7 @@
         <v>9,696 km</v>
       </c>
       <c r="D25" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="str">
         <v>$12,204</v>
@@ -3851,10 +3851,10 @@
         <v>10</v>
       </c>
       <c r="G25" t="str">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H25" t="str">
-        <v>A350-1000 (GRU-VCE 2), A380-800 (GRU-0-3)</v>
+        <v>A380-800 (GRU-0-3)</v>
       </c>
       <c r="I25" t="str">
         <v>1747</v>
@@ -3869,13 +3869,13 @@
         <v>24</v>
       </c>
       <c r="M25" t="str">
-        <v>1747</v>
+        <v>946</v>
       </c>
       <c r="N25" t="str">
-        <v>303</v>
+        <v>244</v>
       </c>
       <c r="O25" t="str">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="P25" t="str">
         <v>24</v>
@@ -3905,13 +3905,13 @@
         <v>24</v>
       </c>
       <c r="Y25" t="str">
-        <v>1747</v>
+        <v>946</v>
       </c>
       <c r="Z25" t="str">
-        <v>303</v>
+        <v>244</v>
       </c>
       <c r="AA25" t="str">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AB25" t="str">
         <v>24</v>
@@ -3935,7 +3935,7 @@
         <v>VCE</v>
       </c>
       <c r="AI25" t="str">
-        <v>A350-1000/GRU-VCE 2,A380-800/GRU-0-3</v>
+        <v>A380-800/GRU-0-3</v>
       </c>
       <c r="AJ25">
         <v>1747</v>
@@ -3950,13 +3950,13 @@
         <v>24</v>
       </c>
       <c r="AN25">
-        <v>1747</v>
+        <v>946</v>
       </c>
       <c r="AO25">
-        <v>303</v>
+        <v>244</v>
       </c>
       <c r="AP25">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AQ25">
         <v>24</v>
@@ -4429,13 +4429,13 @@
         <v>A380-800 (KIX-0-4)</v>
       </c>
       <c r="I29" t="str">
-        <v>1628</v>
+        <v>1677</v>
       </c>
       <c r="J29" t="str">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="K29" t="str">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="L29" t="str">
         <v>27</v>
@@ -4453,25 +4453,25 @@
         <v>27</v>
       </c>
       <c r="Q29" t="str">
-        <v>$2,722</v>
+        <v>$2,612</v>
       </c>
       <c r="R29" t="str">
-        <v>$3,620</v>
+        <v>$3,473</v>
       </c>
       <c r="S29" t="str">
-        <v>$6,260</v>
+        <v>$6,007</v>
       </c>
       <c r="T29" t="str">
-        <v>$4,570</v>
+        <v>$4,571</v>
       </c>
       <c r="U29" t="str">
-        <v>1628</v>
+        <v>1677</v>
       </c>
       <c r="V29" t="str">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="W29" t="str">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="X29" t="str">
         <v>27</v>
@@ -4489,16 +4489,16 @@
         <v>27</v>
       </c>
       <c r="AC29" t="str">
-        <v>$2,722</v>
+        <v>$2,612</v>
       </c>
       <c r="AD29" t="str">
-        <v>$3,620</v>
+        <v>$3,473</v>
       </c>
       <c r="AE29" t="str">
-        <v>$6,260</v>
+        <v>$6,007</v>
       </c>
       <c r="AF29" t="str">
-        <v>$4,570</v>
+        <v>$4,571</v>
       </c>
       <c r="AG29" t="str">
         <v>KIX</v>
@@ -4510,13 +4510,13 @@
         <v>A380-800/KIX-0-4</v>
       </c>
       <c r="AJ29">
-        <v>1628</v>
+        <v>1677</v>
       </c>
       <c r="AK29">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="AL29">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AM29">
         <v>27</v>
@@ -4534,16 +4534,16 @@
         <v>27</v>
       </c>
       <c r="AR29">
-        <v>2722</v>
+        <v>2612</v>
       </c>
       <c r="AS29">
-        <v>3620</v>
+        <v>3473</v>
       </c>
       <c r="AT29">
-        <v>6260</v>
+        <v>6007</v>
       </c>
       <c r="AU29">
-        <v>4570</v>
+        <v>4571</v>
       </c>
     </row>
     <row r="30">
@@ -4584,28 +4584,28 @@
         <v>22</v>
       </c>
       <c r="M30" t="str">
-        <v>902</v>
+        <v>0</v>
       </c>
       <c r="N30" t="str">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="O30" t="str">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="P30" t="str">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="str">
-        <v>$2,506</v>
+        <v>$0</v>
       </c>
       <c r="R30" t="str">
-        <v>$3,332</v>
+        <v>$0</v>
       </c>
       <c r="S30" t="str">
-        <v>$5,763</v>
+        <v>$0</v>
       </c>
       <c r="T30" t="str">
-        <v>$4,448</v>
+        <v>$0</v>
       </c>
       <c r="U30" t="str">
         <v>1878</v>
@@ -5013,28 +5013,28 @@
         <v>28</v>
       </c>
       <c r="M33" t="str">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="N33" t="str">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="O33" t="str">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="P33" t="str">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="str">
-        <v>$2,052</v>
+        <v>$0</v>
       </c>
       <c r="R33" t="str">
-        <v>$2,660</v>
+        <v>$0</v>
       </c>
       <c r="S33" t="str">
-        <v>$4,424</v>
+        <v>$0</v>
       </c>
       <c r="T33" t="str">
-        <v>$3,642</v>
+        <v>$0</v>
       </c>
       <c r="U33" t="str">
         <v>1696</v>
@@ -5299,28 +5299,28 @@
         <v>21</v>
       </c>
       <c r="M35" t="str">
-        <v>1660</v>
+        <v>0</v>
       </c>
       <c r="N35" t="str">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="O35" t="str">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P35" t="str">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="str">
-        <v>$2,208</v>
+        <v>$0</v>
       </c>
       <c r="R35" t="str">
-        <v>$2,937</v>
+        <v>$0</v>
       </c>
       <c r="S35" t="str">
-        <v>$5,078</v>
+        <v>$0</v>
       </c>
       <c r="T35" t="str">
-        <v>$3,817</v>
+        <v>$0</v>
       </c>
       <c r="U35" t="str">
         <v>1782</v>
@@ -5585,16 +5585,16 @@
         <v>30</v>
       </c>
       <c r="M37" t="str">
-        <v>1206</v>
+        <v>608</v>
       </c>
       <c r="N37" t="str">
-        <v>356</v>
+        <v>42</v>
       </c>
       <c r="O37" t="str">
-        <v>132</v>
+        <v>4</v>
       </c>
       <c r="P37" t="str">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="str">
         <v>$2,459</v>
@@ -5606,7 +5606,7 @@
         <v>$5,655</v>
       </c>
       <c r="T37" t="str">
-        <v>$4,312</v>
+        <v>$0</v>
       </c>
       <c r="U37" t="str">
         <v>1797</v>
@@ -5871,28 +5871,28 @@
         <v>30</v>
       </c>
       <c r="M39" t="str">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="N39" t="str">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="O39" t="str">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P39" t="str">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="str">
-        <v>$2,694</v>
+        <v>$0</v>
       </c>
       <c r="R39" t="str">
-        <v>$3,583</v>
+        <v>$0</v>
       </c>
       <c r="S39" t="str">
-        <v>$6,196</v>
+        <v>$0</v>
       </c>
       <c r="T39" t="str">
-        <v>$4,577</v>
+        <v>$0</v>
       </c>
       <c r="U39" t="str">
         <v>1547</v>
@@ -6014,28 +6014,28 @@
         <v>24</v>
       </c>
       <c r="M40" t="str">
-        <v>1730</v>
+        <v>0</v>
       </c>
       <c r="N40" t="str">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="O40" t="str">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="P40" t="str">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="str">
-        <v>$2,198</v>
+        <v>$0</v>
       </c>
       <c r="R40" t="str">
-        <v>$2,923</v>
+        <v>$0</v>
       </c>
       <c r="S40" t="str">
-        <v>$5,055</v>
+        <v>$0</v>
       </c>
       <c r="T40" t="str">
-        <v>$3,733</v>
+        <v>$0</v>
       </c>
       <c r="U40" t="str">
         <v>1903</v>
@@ -6157,28 +6157,28 @@
         <v>23</v>
       </c>
       <c r="M41" t="str">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="N41" t="str">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="O41" t="str">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P41" t="str">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="str">
-        <v>$2,191</v>
+        <v>$0</v>
       </c>
       <c r="R41" t="str">
-        <v>$2,848</v>
+        <v>$0</v>
       </c>
       <c r="S41" t="str">
-        <v>$4,753</v>
+        <v>$0</v>
       </c>
       <c r="T41" t="str">
-        <v>$3,888</v>
+        <v>$0</v>
       </c>
       <c r="U41" t="str">
         <v>1457</v>
@@ -6443,28 +6443,28 @@
         <v>27</v>
       </c>
       <c r="M43" t="str">
-        <v>634</v>
+        <v>0</v>
       </c>
       <c r="N43" t="str">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O43" t="str">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="P43" t="str">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="str">
-        <v>$2,300</v>
+        <v>$0</v>
       </c>
       <c r="R43" t="str">
-        <v>$2,988</v>
+        <v>$0</v>
       </c>
       <c r="S43" t="str">
-        <v>$4,980</v>
+        <v>$0</v>
       </c>
       <c r="T43" t="str">
-        <v>$4,084</v>
+        <v>$0</v>
       </c>
       <c r="U43" t="str">
         <v>1474</v>
@@ -7861,13 +7861,13 @@
         <v>787-9 (LAX-AMS 2), A380-800 (LASV-AMSTERDAM)</v>
       </c>
       <c r="I53" t="str">
-        <v>1536</v>
+        <v>1544</v>
       </c>
       <c r="J53" t="str">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K53" t="str">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L53" t="str">
         <v>32</v>
@@ -7897,13 +7897,13 @@
         <v>$0</v>
       </c>
       <c r="U53" t="str">
-        <v>1536</v>
+        <v>1544</v>
       </c>
       <c r="V53" t="str">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="W53" t="str">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="X53" t="str">
         <v>32</v>
@@ -7921,16 +7921,16 @@
         <v>32</v>
       </c>
       <c r="AC53" t="str">
-        <v>$2,612</v>
+        <v>$2,570</v>
       </c>
       <c r="AD53" t="str">
-        <v>$3,473</v>
+        <v>$3,418</v>
       </c>
       <c r="AE53" t="str">
-        <v>$6,007</v>
+        <v>$5,910</v>
       </c>
       <c r="AF53" t="str">
-        <v>$4,419</v>
+        <v>$4,411</v>
       </c>
       <c r="AG53" t="str">
         <v>LAX</v>
@@ -7942,13 +7942,13 @@
         <v>787-9/LAX-AMS 2,A380-800/LASV-AMSTERDAM</v>
       </c>
       <c r="AJ53">
-        <v>1536</v>
+        <v>1544</v>
       </c>
       <c r="AK53">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AL53">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM53">
         <v>32</v>
@@ -7966,16 +7966,16 @@
         <v>32</v>
       </c>
       <c r="AR53">
-        <v>2612</v>
+        <v>2570</v>
       </c>
       <c r="AS53">
-        <v>3473</v>
+        <v>3418</v>
       </c>
       <c r="AT53">
-        <v>6007</v>
+        <v>5910</v>
       </c>
       <c r="AU53">
-        <v>4419</v>
+        <v>4411</v>
       </c>
     </row>
     <row r="54">
@@ -8159,28 +8159,28 @@
         <v>30</v>
       </c>
       <c r="M55" t="str">
-        <v>578</v>
+        <v>0</v>
       </c>
       <c r="N55" t="str">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="O55" t="str">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="P55" t="str">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="str">
-        <v>$2,741</v>
+        <v>$0</v>
       </c>
       <c r="R55" t="str">
-        <v>$3,645</v>
+        <v>$0</v>
       </c>
       <c r="S55" t="str">
-        <v>$6,303</v>
+        <v>$0</v>
       </c>
       <c r="T55" t="str">
-        <v>$4,748</v>
+        <v>$0</v>
       </c>
       <c r="U55" t="str">
         <v>1406</v>
@@ -8302,25 +8302,25 @@
         <v>30</v>
       </c>
       <c r="M56" t="str">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N56" t="str">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="O56" t="str">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="P56" t="str">
         <v>0</v>
       </c>
       <c r="Q56" t="str">
-        <v>$2,704</v>
+        <v>$0</v>
       </c>
       <c r="R56" t="str">
-        <v>$3,596</v>
+        <v>$0</v>
       </c>
       <c r="S56" t="str">
-        <v>$6,219</v>
+        <v>$0</v>
       </c>
       <c r="T56" t="str">
         <v>$0</v>
@@ -8588,28 +8588,28 @@
         <v>28</v>
       </c>
       <c r="M58" t="str">
-        <v>588</v>
+        <v>0</v>
       </c>
       <c r="N58" t="str">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="O58" t="str">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="P58" t="str">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="str">
-        <v>$2,658</v>
+        <v>$0</v>
       </c>
       <c r="R58" t="str">
-        <v>$3,535</v>
+        <v>$0</v>
       </c>
       <c r="S58" t="str">
-        <v>$6,113</v>
+        <v>$0</v>
       </c>
       <c r="T58" t="str">
-        <v>$4,564</v>
+        <v>$0</v>
       </c>
       <c r="U58" t="str">
         <v>1707</v>
@@ -8874,25 +8874,25 @@
         <v>29</v>
       </c>
       <c r="M60" t="str">
-        <v>680</v>
+        <v>0</v>
       </c>
       <c r="N60" t="str">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="O60" t="str">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="P60" t="str">
         <v>0</v>
       </c>
       <c r="Q60" t="str">
-        <v>$2,589</v>
+        <v>$0</v>
       </c>
       <c r="R60" t="str">
-        <v>$3,443</v>
+        <v>$0</v>
       </c>
       <c r="S60" t="str">
-        <v>$5,954</v>
+        <v>$0</v>
       </c>
       <c r="T60" t="str">
         <v>$0</v>
@@ -9160,28 +9160,28 @@
         <v>20</v>
       </c>
       <c r="M62" t="str">
-        <v>958</v>
+        <v>0</v>
       </c>
       <c r="N62" t="str">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="O62" t="str">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P62" t="str">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="str">
-        <v>$2,731</v>
+        <v>$0</v>
       </c>
       <c r="R62" t="str">
-        <v>$3,632</v>
+        <v>$0</v>
       </c>
       <c r="S62" t="str">
-        <v>$6,281</v>
+        <v>$0</v>
       </c>
       <c r="T62" t="str">
-        <v>$4,689</v>
+        <v>$0</v>
       </c>
       <c r="U62" t="str">
         <v>1243</v>
@@ -9589,25 +9589,25 @@
         <v>27</v>
       </c>
       <c r="M65" t="str">
-        <v>790</v>
+        <v>0</v>
       </c>
       <c r="N65" t="str">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="O65" t="str">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P65" t="str">
         <v>0</v>
       </c>
       <c r="Q65" t="str">
-        <v>$2,585</v>
+        <v>$0</v>
       </c>
       <c r="R65" t="str">
-        <v>$3,438</v>
+        <v>$0</v>
       </c>
       <c r="S65" t="str">
-        <v>$5,945</v>
+        <v>$0</v>
       </c>
       <c r="T65" t="str">
         <v>$0</v>
@@ -9714,10 +9714,10 @@
         <v>10</v>
       </c>
       <c r="G66" t="str">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H66" t="str">
-        <v>A380-800 (LAX-HKG 2), A380-800 (LAX-HKG 1)</v>
+        <v>777-300ER (LAX-0), A380-800 (LAX-HKG 1)</v>
       </c>
       <c r="I66" t="str">
         <v>2088</v>
@@ -9732,28 +9732,28 @@
         <v>32</v>
       </c>
       <c r="M66" t="str">
-        <v>1870</v>
+        <v>0</v>
       </c>
       <c r="N66" t="str">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="O66" t="str">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="P66" t="str">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="str">
-        <v>$3,345</v>
+        <v>$0</v>
       </c>
       <c r="R66" t="str">
-        <v>$4,448</v>
+        <v>$0</v>
       </c>
       <c r="S66" t="str">
-        <v>$7,693</v>
+        <v>$0</v>
       </c>
       <c r="T66" t="str">
-        <v>$5,684</v>
+        <v>$0</v>
       </c>
       <c r="U66" t="str">
         <v>2088</v>
@@ -9768,13 +9768,13 @@
         <v>32</v>
       </c>
       <c r="Y66" t="str">
-        <v>1870</v>
+        <v>1666</v>
       </c>
       <c r="Z66" t="str">
-        <v>478</v>
+        <v>348</v>
       </c>
       <c r="AA66" t="str">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="AB66" t="str">
         <v>32</v>
@@ -9798,7 +9798,7 @@
         <v>HKG</v>
       </c>
       <c r="AI66" t="str">
-        <v>A380-800/LAX-HKG 2,A380-800/LAX-HKG 1</v>
+        <v>777-300ER/LAX-0,A380-800/LAX-HKG 1</v>
       </c>
       <c r="AJ66">
         <v>2088</v>
@@ -9813,13 +9813,13 @@
         <v>32</v>
       </c>
       <c r="AN66">
-        <v>1870</v>
+        <v>1666</v>
       </c>
       <c r="AO66">
-        <v>478</v>
+        <v>348</v>
       </c>
       <c r="AP66">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="AQ66">
         <v>32</v>
@@ -9875,28 +9875,28 @@
         <v>30</v>
       </c>
       <c r="M67" t="str">
-        <v>578</v>
+        <v>0</v>
       </c>
       <c r="N67" t="str">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="O67" t="str">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="P67" t="str">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="str">
-        <v>$2,753</v>
+        <v>$0</v>
       </c>
       <c r="R67" t="str">
-        <v>$3,661</v>
+        <v>$0</v>
       </c>
       <c r="S67" t="str">
-        <v>$6,331</v>
+        <v>$0</v>
       </c>
       <c r="T67" t="str">
-        <v>$4,726</v>
+        <v>$0</v>
       </c>
       <c r="U67" t="str">
         <v>1739</v>
@@ -10018,25 +10018,25 @@
         <v>31</v>
       </c>
       <c r="M68" t="str">
-        <v>1130</v>
+        <v>0</v>
       </c>
       <c r="N68" t="str">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="O68" t="str">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="P68" t="str">
         <v>0</v>
       </c>
       <c r="Q68" t="str">
-        <v>$2,552</v>
+        <v>$0</v>
       </c>
       <c r="R68" t="str">
-        <v>$3,394</v>
+        <v>$0</v>
       </c>
       <c r="S68" t="str">
-        <v>$5,869</v>
+        <v>$0</v>
       </c>
       <c r="T68" t="str">
         <v>$0</v>
@@ -10447,13 +10447,13 @@
         <v>32</v>
       </c>
       <c r="M71" t="str">
-        <v>1422</v>
+        <v>578</v>
       </c>
       <c r="N71" t="str">
-        <v>564</v>
+        <v>314</v>
       </c>
       <c r="O71" t="str">
-        <v>232</v>
+        <v>134</v>
       </c>
       <c r="P71" t="str">
         <v>32</v>
@@ -10590,28 +10590,28 @@
         <v>22</v>
       </c>
       <c r="M72" t="str">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="N72" t="str">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="O72" t="str">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P72" t="str">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="str">
-        <v>$2,781</v>
+        <v>$0</v>
       </c>
       <c r="R72" t="str">
-        <v>$3,698</v>
+        <v>$0</v>
       </c>
       <c r="S72" t="str">
-        <v>$6,396</v>
+        <v>$0</v>
       </c>
       <c r="T72" t="str">
-        <v>$4,775</v>
+        <v>$0</v>
       </c>
       <c r="U72" t="str">
         <v>1306</v>
@@ -11019,16 +11019,16 @@
         <v>32</v>
       </c>
       <c r="M75" t="str">
-        <v>1272</v>
+        <v>694</v>
       </c>
       <c r="N75" t="str">
-        <v>398</v>
+        <v>84</v>
       </c>
       <c r="O75" t="str">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="P75" t="str">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="str">
         <v>$2,514</v>
@@ -11040,7 +11040,7 @@
         <v>$5,782</v>
       </c>
       <c r="T75" t="str">
-        <v>$4,316</v>
+        <v>$0</v>
       </c>
       <c r="U75" t="str">
         <v>1649</v>
@@ -11162,13 +11162,13 @@
         <v>25</v>
       </c>
       <c r="M76" t="str">
-        <v>1312</v>
+        <v>542</v>
       </c>
       <c r="N76" t="str">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="O76" t="str">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="P76" t="str">
         <v>25</v>

--- a/routes_output.xlsx
+++ b/routes_output.xlsx
@@ -653,42 +653,42 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>$2,768</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>$3,682</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>$6,366</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>$4,795</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,17 +835,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>$2,356</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>$3,133</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>$5,418</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>$2,735</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>$3,637</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>$6,289</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1301,42 +1301,42 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>$2,093</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>$2,715</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>$4,516</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>$3,663</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1483,17 +1483,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>$2,668</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>$3,548</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>$6,135</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1625,42 +1625,42 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>$2,170</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>$2,886</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>$4,991</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>$3,796</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1807,17 +1807,17 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>$2,234</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>$2,971</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>$5,138</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1949,42 +1949,42 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>$2,197</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>$2,921</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>$5,051</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>$3,803</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -2111,42 +2111,42 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>$2,742</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>$3,646</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>$6,306</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>$4,799</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -2435,17 +2435,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2455,17 +2455,17 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>$2,732</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>$3,634</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>$6,284</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>$2,704</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>$3,596</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>$6,219</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2941,17 +2941,17 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>$1,981</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>$2,635</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>$4,556</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -3083,42 +3083,42 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>$1,901</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>$2,528</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>$4,372</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>$3,290</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -3245,42 +3245,42 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>$2,609</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>$3,470</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>$6,001</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>$4,519</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -3407,42 +3407,42 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>$2,590</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>$3,444</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>$5,955</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>$4,484</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3569,42 +3569,42 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>$2,662</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>$3,540</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>$6,122</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>$4,659</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3731,42 +3731,42 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>$2,633</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>$3,502</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>$6,055</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>$4,560</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3893,42 +3893,42 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>$2,382</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>$3,168</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>$5,478</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>$4,046</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -4055,42 +4055,42 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>$2,758</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>$3,667</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>$6,341</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>$4,776</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -4379,42 +4379,42 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>$2,718</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>$3,614</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>$6,251</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>$4,758</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4561,17 +4561,17 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>$2,415</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>$3,212</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>$5,553</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>$2,723</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>$3,622</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>$6,262</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4997,27 +4997,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>A380-800 (KIX-0-4)</t>
+          <t>747-400 (KIX-ATH 2), A380-800 (KIX-0-4)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>397</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -5027,102 +5027,102 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1658</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>$2,722</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>$3,620</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>$6,260</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>$4,570</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1628</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>1658</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>$2,722</t>
+          <t>$2,706</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>$3,620</t>
+          <t>$3,598</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>$6,260</t>
+          <t>$6,223</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>$4,570</t>
+          <t>$4,580</t>
         </is>
       </c>
     </row>
@@ -5189,42 +5189,42 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>$2,506</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>$3,332</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>$5,763</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>$4,448</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -5351,77 +5351,77 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>$2,483</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>$3,302</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>$5,710</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>$4,353</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>1755</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>1614</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>144</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5483,132 +5483,132 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>A380-800 (KIX-BUDAPEST)</t>
+          <t>777-300ER (KIX-BUD 2), A380-800 (KIX-BUDAPEST)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>321</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>$2,200</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>$2,860</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>$4,775</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>$3,904</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>321</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>97</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>$2,200</t>
+          <t>$2,598</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>$2,860</t>
+          <t>$3,455</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>$4,775</t>
+          <t>$5,975</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>$3,904</t>
+          <t>$4,396</t>
         </is>
       </c>
     </row>
@@ -5675,42 +5675,42 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>$2,052</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>$2,660</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>$4,424</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>$3,642</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5837,42 +5837,42 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>$2,151</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>$2,860</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>$4,947</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>$3,763</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5999,42 +5999,42 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>$2,208</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>$2,937</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>$5,078</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>$3,817</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -6323,17 +6323,17 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>$2,459</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>$3,270</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>$5,655</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -6545,42 +6545,42 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>$2,273</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>$3,023</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>$5,227</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>$3,977</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -6647,42 +6647,42 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>$2,694</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>$3,583</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>$6,196</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>$4,577</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -6809,42 +6809,42 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>$2,198</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>$2,923</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>$5,055</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>$3,733</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6941,132 +6941,132 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>A380-800 (KIX-LEIPZIG)</t>
+          <t>A330-900 (KIX-LEJ 2), A380-800 (KIX-LEIPZIG)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>323</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>107</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>$2,191</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>$2,848</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>$4,753</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>$3,888</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>323</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>107</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>323</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>$2,191</t>
+          <t>$2,616</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>$2,848</t>
+          <t>$3,479</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>$4,753</t>
+          <t>$6,016</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>$3,888</t>
+          <t>$4,427</t>
         </is>
       </c>
     </row>
@@ -7133,42 +7133,42 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>$2,219</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>$2,881</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>$4,800</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>$3,939</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -7265,132 +7265,132 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A380-800 (KIX-LYON)</t>
+          <t>747-400 (KIX-LYS 2), A380-800 (KIX-LYON)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>432</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>160</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>$2,300</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>$2,988</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>$4,980</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>$4,084</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>432</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>432</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>$2,300</t>
+          <t>$2,707</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>$2,988</t>
+          <t>$3,600</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>$4,980</t>
+          <t>$6,226</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>$4,084</t>
+          <t>$4,805</t>
         </is>
       </c>
     </row>
@@ -7457,42 +7457,42 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>$2,280</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>$3,033</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>$5,244</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>$3,997</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -7913,22 +7913,22 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>A380-800 (KIX-PRAGUE)</t>
+          <t>747-400 (KIX-PRG 2), A380-800 (KIX-PRAGUE)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>339</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -7943,102 +7943,102 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>$2,602</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>$3,460</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>$5,984</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>$4,420</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>1809</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>$2,602</t>
+          <t>$2,617</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>$3,460</t>
+          <t>$3,480</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>$5,984</t>
+          <t>$6,019</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>$4,420</t>
+          <t>$4,428</t>
         </is>
       </c>
     </row>
@@ -8105,42 +8105,42 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>$2,444</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>$3,251</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>$5,621</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>$4,286</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -8237,27 +8237,27 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>A380-800 (KIX-SOFIA)</t>
+          <t>777-300ER (KIX-SOF 2), A380-800 (KIX-SOFIA)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>274</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -8307,17 +8307,17 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>274</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -8327,17 +8327,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>274</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -8347,22 +8347,22 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>$2,526</t>
+          <t>$2,623</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>$3,359</t>
+          <t>$3,488</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>$5,809</t>
+          <t>$6,032</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>$4,429</t>
+          <t>$4,438</t>
         </is>
       </c>
     </row>
@@ -8429,42 +8429,42 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>$2,060</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>$2,739</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>$4,738</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>$3,654</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -8591,42 +8591,42 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>$2,206</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>$3,021</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>$5,225</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>$3,859</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -8753,102 +8753,102 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
         <is>
           <t>$2,120</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>$2,819</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="AE52" t="inlineStr">
         <is>
           <t>$4,875</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>$2,120</t>
-        </is>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>$2,819</t>
-        </is>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>$4,875</t>
-        </is>
-      </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>$3,671</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -8975,42 +8975,42 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>$2,612</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>$3,473</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>$6,007</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>$4,419</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -9077,102 +9077,102 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>870</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>$2,571</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>$3,419</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="AE54" t="inlineStr">
         <is>
           <t>$5,913</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>1429</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>$2,571</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>$3,419</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>$5,913</t>
-        </is>
-      </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>$4,367</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -9239,42 +9239,42 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>$2,741</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>$3,645</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>$6,303</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>$4,748</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -9563,42 +9563,42 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>$2,596</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>$3,452</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>$5,970</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>$4,457</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -9725,42 +9725,42 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>$2,658</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>$3,535</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>$6,113</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>$4,564</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -9887,77 +9887,77 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
           <t>578</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>134</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>$2,610</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>$3,471</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>$6,002</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>$4,480</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>200</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -10211,72 +10211,72 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
           <t>620</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>314</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>$2,808</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>$3,734</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>$6,458</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>$4,820</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>326</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -10373,42 +10373,42 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>$2,731</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>$3,632</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>$6,281</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>$4,689</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -10535,42 +10535,42 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>$2,669</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>$3,549</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>$6,138</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>$4,582</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -10697,77 +10697,77 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>$2,833</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>$3,767</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>$6,515</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>$4,863</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>608</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>314</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -11021,102 +11021,102 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
           <t>1304</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
         <is>
           <t>$3,345</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="AD66" t="inlineStr">
         <is>
           <t>$4,448</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="AE66" t="inlineStr">
         <is>
           <t>$7,693</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>$3,345</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>$4,448</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>$7,693</t>
-        </is>
-      </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>$5,684</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -11183,77 +11183,77 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
           <t>578</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>134</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>$2,753</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>$3,661</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>$6,331</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>$4,726</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>1739</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>142</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -11345,17 +11345,17 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -11365,17 +11365,17 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>$2,552</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>$3,394</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>$5,869</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -11507,77 +11507,77 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
           <t>578</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>134</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>$2,516</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>$3,346</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>$5,786</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>$4,318</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>1096</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>170</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -11729,22 +11729,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>938</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>$4,495</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -11831,42 +11831,42 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>$2,687</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>$3,573</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>$6,180</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>$4,612</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -11993,42 +11993,42 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>$2,781</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>$3,698</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>$6,396</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>$4,775</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -12155,102 +12155,102 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>1493</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>950</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>232</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
         <is>
           <t>$2,750</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="AD73" t="inlineStr">
         <is>
           <t>$3,657</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="AE73" t="inlineStr">
         <is>
           <t>$6,324</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>1493</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>1493</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>$2,750</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>$3,657</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>$6,324</t>
-        </is>
-      </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>$4,721</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -12317,17 +12317,17 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -12337,17 +12337,17 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>$2,801</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>$3,725</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>$6,442</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -12479,17 +12479,17 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -12499,17 +12499,17 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>$2,514</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>$3,343</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>$5,782</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -12641,42 +12641,42 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>$2,581</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>$3,432</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>$5,936</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>$4,431</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -12803,42 +12803,42 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>$2,455</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>$3,265</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>$4,445</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>$3,641</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -12965,77 +12965,77 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>132</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>$2,578</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>$3,428</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>$5,929</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>$4,425</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>156</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -13127,42 +13127,42 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>$2,815</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>$3,743</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>$6,474</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>$4,833</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -13289,17 +13289,17 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -13309,17 +13309,17 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>$2,762</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>$3,673</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>$6,352</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">

--- a/routes_output.xlsx
+++ b/routes_output.xlsx
@@ -653,42 +653,42 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>346</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,768</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,682</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,366</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,795</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -815,42 +815,42 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>308</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>106</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,356</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,133</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,418</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,002</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -977,42 +977,42 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>332</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,735</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,637</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,289</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,736</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1139,42 +1139,42 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>764</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,825</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,757</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,497</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,800</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1301,42 +1301,42 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>952</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,093</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,715</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,516</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,663</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1463,42 +1463,42 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,668</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,548</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,135</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,620</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1625,42 +1625,42 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>376</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,170</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,886</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,991</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,796</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1787,37 +1787,37 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,234</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,971</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,138</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1949,42 +1949,42 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>566</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>344</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,197</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,921</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,051</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,803</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -2111,42 +2111,42 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>580</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,742</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,646</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,306</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,799</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -2435,44 +2435,44 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>$2,732</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>$3,634</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>$6,284</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>1526</t>
@@ -2495,17 +2495,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>262</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2759,37 +2759,37 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,704</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,596</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,219</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2921,42 +2921,42 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>396</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$1,981</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,635</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,556</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,429</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -3083,42 +3083,42 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>656</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>290</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$1,901</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,528</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,372</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,290</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -3245,42 +3245,42 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,609</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,470</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,001</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,519</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -3407,42 +3407,42 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>346</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>118</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,590</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,444</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,955</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,484</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3569,42 +3569,42 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>842</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>274</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,662</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,540</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,122</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,659</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3731,42 +3731,42 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,633</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,502</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,055</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,560</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3893,42 +3893,42 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,382</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,168</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,478</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,046</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -4055,42 +4055,42 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>750</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,758</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,667</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,341</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,776</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -4217,42 +4217,42 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>780</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,287</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,042</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,260</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,954</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -4379,42 +4379,42 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>93</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,718</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,614</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,251</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,758</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4541,37 +4541,37 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,415</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,212</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,553</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -4865,37 +4865,37 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,723</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,622</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,262</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -5027,42 +5027,42 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>790</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>284</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,706</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,598</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,223</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,580</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -5189,42 +5189,42 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>902</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,506</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,332</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,763</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,448</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -5351,42 +5351,42 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,483</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,302</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,710</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,353</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -5513,42 +5513,42 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>321</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,598</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,455</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,975</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,396</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -5675,42 +5675,42 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>692</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>278</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,052</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,660</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,424</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,642</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -5807,27 +5807,27 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>A380-800 (KIX-0-3), 767-300ER (KIX-DXB 2)</t>
+          <t>A380-800 (KIX-0-3), 767-300ER (KIX-DXB 2), A350-900ULR (KIX-DXB 2)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>403</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -5837,57 +5837,57 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>748</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>298</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,228</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,963</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,124</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,770</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>403</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5917,22 +5917,22 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>$2,151</t>
+          <t>$2,228</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>$2,860</t>
+          <t>$2,963</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>$4,947</t>
+          <t>$5,124</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>$3,763</t>
+          <t>$3,770</t>
         </is>
       </c>
     </row>
@@ -5999,42 +5999,42 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,208</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,937</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,078</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,817</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -6323,42 +6323,42 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>356</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>132</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,459</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,270</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,655</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,312</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6455,22 +6455,22 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>A380-800 (KIX-0-2)</t>
+          <t>777-300ER (KIX-KBP 2), A380-800 (KIX-0-2)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>273</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6485,52 +6485,52 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
+          <t>$2,355</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>$3,132</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>$5,416</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>273</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -6545,42 +6545,42 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,355</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,132</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,416</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,985</t>
         </is>
       </c>
     </row>
@@ -6647,42 +6647,42 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>720</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,694</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,583</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,196</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,577</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -6809,42 +6809,42 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>274</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,198</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,923</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,055</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,733</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -6971,42 +6971,42 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>323</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,616</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,479</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,016</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,427</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -7133,42 +7133,42 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,219</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,881</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,800</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,939</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -7295,42 +7295,42 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>432</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,707</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,600</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,226</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,805</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -7457,42 +7457,42 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,280</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,033</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,244</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,997</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -7943,42 +7943,42 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>339</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>106</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,617</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,480</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,019</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,428</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -8105,42 +8105,42 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,444</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,251</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,621</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,286</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -8267,37 +8267,37 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,623</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,488</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,032</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -8429,42 +8429,42 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>808</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>62</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,060</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,739</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,738</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,654</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -8591,42 +8591,42 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>648</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>296</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,206</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,021</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,225</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,859</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -8753,44 +8753,44 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
+          <t>$2,120</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>$2,819</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>$4,875</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>2171</t>
@@ -8813,22 +8813,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>224</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,671</t>
         </is>
       </c>
     </row>
@@ -8975,42 +8975,42 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,612</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,473</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,007</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,419</t>
         </is>
       </c>
     </row>
@@ -9077,44 +9077,44 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
+          <t>$2,571</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>$3,419</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>$5,913</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>1429</t>
@@ -9137,22 +9137,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,367</t>
         </is>
       </c>
     </row>
@@ -9239,42 +9239,42 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,741</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,645</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,303</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,748</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -9401,37 +9401,37 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,704</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,596</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,219</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -9563,42 +9563,42 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>984</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>398</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>162</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,596</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,452</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,970</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,457</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -9725,42 +9725,42 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>336</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,658</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,535</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,113</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,564</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -9887,42 +9887,42 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,610</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,471</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,002</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,480</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -9947,17 +9947,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>906</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -10049,37 +10049,37 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,589</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,443</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,954</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -10211,42 +10211,42 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>620</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,808</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,734</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,458</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,820</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -10373,42 +10373,42 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>958</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,731</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,632</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,281</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,689</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -10535,42 +10535,42 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,669</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,549</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,138</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,582</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -10697,42 +10697,42 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>352</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>126</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,833</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,767</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,515</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,863</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -10757,17 +10757,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>352</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -10859,37 +10859,37 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,585</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,438</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,945</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -11021,42 +11021,42 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>478</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>162</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,345</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,448</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$7,693</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,684</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -11081,22 +11081,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>162</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,684</t>
         </is>
       </c>
     </row>
@@ -11183,42 +11183,42 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,753</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,661</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,331</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,726</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -11243,17 +11243,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>354</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -11345,37 +11345,37 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,552</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,394</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,869</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -11507,42 +11507,42 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,516</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,346</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,786</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,318</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -11567,17 +11567,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>408</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -11669,44 +11669,44 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q70" t="inlineStr">
         <is>
+          <t>$2,646</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>$3,519</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>$6,085</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>1490</t>
@@ -11729,22 +11729,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>442</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,495</t>
         </is>
       </c>
     </row>
@@ -11831,42 +11831,42 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>564</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,687</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,573</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,180</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,612</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -11993,42 +11993,42 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>800</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,781</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,698</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,396</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,775</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -12155,44 +12155,44 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
+          <t>$2,750</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>$3,657</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>$6,324</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>1493</t>
@@ -12215,22 +12215,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>546</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,721</t>
         </is>
       </c>
     </row>
@@ -12317,42 +12317,42 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>504</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,801</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,725</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,442</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,759</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -12479,42 +12479,42 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>398</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,514</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,343</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,782</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,316</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -12641,42 +12641,42 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>364</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,581</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,432</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,936</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,431</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -12803,42 +12803,42 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>364</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>154</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,455</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,265</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,445</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,641</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -12965,42 +12965,42 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>538</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>132</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,578</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,428</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,929</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,425</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -13025,17 +13025,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -13127,42 +13127,42 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>454</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,815</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,743</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,474</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,833</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -13289,42 +13289,42 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>424</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,762</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,673</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,352</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,741</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">

--- a/routes_output.xlsx
+++ b/routes_output.xlsx
@@ -1139,17 +1139,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>282</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>95</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1787,22 +1787,22 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>418</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>143</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,916</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1949,17 +1949,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>416</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>146</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>416</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>144</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2273,42 +2273,42 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>866</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>186</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,742</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,647</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,307</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,750</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2435,17 +2435,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2455,17 +2455,17 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>$2,732</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>$3,634</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>$6,284</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>$2,704</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>$3,596</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>$6,219</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2921,42 +2921,42 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>$1,981</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>$2,635</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>$4,556</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>$3,429</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -3083,42 +3083,42 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>$1,901</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>$2,528</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>$4,372</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>$3,290</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -3245,42 +3245,42 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>$2,609</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>$3,470</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>$6,001</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>$4,519</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -3407,42 +3407,42 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>$2,590</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>$3,444</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>$5,955</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>$4,484</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3569,42 +3569,42 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>$2,662</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>$3,540</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>$6,122</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>$4,659</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3731,42 +3731,42 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>$2,633</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>$3,502</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>$6,055</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>$4,560</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3893,42 +3893,42 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>$2,382</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>$3,168</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>$5,478</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>$4,046</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -4055,42 +4055,42 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>$2,758</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>$3,667</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>$6,341</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>$4,776</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -4217,42 +4217,42 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>$2,287</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>$3,042</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>$5,260</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>$3,954</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -4379,42 +4379,42 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>$2,718</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>$3,614</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>$6,251</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>$4,758</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4561,17 +4561,17 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>$2,415</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>$3,212</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>$5,553</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -4763,42 +4763,42 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>$2,624</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>$3,489</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>$6,035</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>$4,653</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -4865,17 +4865,17 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4885,17 +4885,17 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>$2,723</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>$3,622</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>$6,262</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -5027,42 +5027,42 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>$2,706</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>$3,598</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>$6,223</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>$4,580</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -5189,42 +5189,42 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>$2,506</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>$3,332</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>$5,763</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>$4,448</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -5351,77 +5351,77 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>$2,483</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>$3,302</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>$5,710</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>$4,353</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>1755</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>1614</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>144</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -5513,42 +5513,42 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>$2,598</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>$3,455</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>$5,975</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>$4,396</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -5675,42 +5675,42 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>$2,052</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>$2,660</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>$4,424</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>$3,642</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5837,77 +5837,77 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>$2,228</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>$2,963</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>$5,124</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>$3,770</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>320</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5999,42 +5999,42 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>$2,208</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>$2,937</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>$5,078</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>$3,817</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>708</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -6303,17 +6303,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>466</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>166</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -6323,102 +6323,102 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1775</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
           <t>1206</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>356</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>$2,459</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>$3,270</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>$5,655</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>$4,312</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>1797</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>356</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>$2,459</t>
+          <t>$2,553</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>$3,270</t>
+          <t>$3,395</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>$5,655</t>
+          <t>$5,871</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>$4,312</t>
+          <t>$4,320</t>
         </is>
       </c>
     </row>
@@ -6485,102 +6485,102 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
           <t>848</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
         <is>
           <t>$2,355</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>$3,132</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>$5,416</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>1917</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>$2,355</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>$3,132</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>$5,416</t>
-        </is>
-      </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>$3,985</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -6647,42 +6647,42 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>$2,694</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>$3,583</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>$6,196</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>$4,577</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -6809,42 +6809,42 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>$2,198</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>$2,923</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>$5,055</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>$3,733</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -6971,42 +6971,42 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>$2,616</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>$3,479</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>$6,016</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>$4,427</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -7133,42 +7133,42 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>$2,219</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>$2,881</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>$4,800</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>$3,939</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -7295,42 +7295,42 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>$2,707</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>$3,600</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>$6,226</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>$4,805</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -7457,42 +7457,42 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>$2,280</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>$3,033</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>$5,244</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>$3,997</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -7943,42 +7943,42 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>$2,617</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>$3,480</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>$6,019</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>$4,428</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -8105,42 +8105,42 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>$2,444</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>$3,251</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>$5,621</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>$4,286</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -8267,17 +8267,17 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -8287,17 +8287,17 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>$2,623</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>$3,488</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>$6,032</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -8429,77 +8429,77 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
           <t>808</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>226</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>$2,060</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>$2,739</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>$4,738</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>$3,654</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>84</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -8591,42 +8591,42 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>$2,206</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>$3,021</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>$5,225</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>$3,859</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -8753,102 +8753,102 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
         <is>
           <t>$2,120</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>$2,819</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="AE52" t="inlineStr">
         <is>
           <t>$4,875</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>$2,120</t>
-        </is>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>$2,819</t>
-        </is>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>$4,875</t>
-        </is>
-      </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>$3,671</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -8975,42 +8975,42 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>$2,612</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>$3,473</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>$6,007</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>$4,419</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -9077,102 +9077,102 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>870</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>$2,571</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>$3,419</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="AE54" t="inlineStr">
         <is>
           <t>$5,913</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>1429</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>$2,571</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>$3,419</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>$5,913</t>
-        </is>
-      </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>$4,367</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -9239,42 +9239,42 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>$2,741</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>$3,645</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>$6,303</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>$4,748</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -9401,102 +9401,102 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
         <is>
           <t>$2,704</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="AD56" t="inlineStr">
         <is>
           <t>$3,596</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="AE56" t="inlineStr">
         <is>
           <t>$6,219</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>537</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>$2,704</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>$3,596</t>
-        </is>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>$6,219</t>
-        </is>
-      </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>$4,594</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -9563,42 +9563,42 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>$2,596</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>$3,452</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>$5,970</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>$4,457</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -9725,42 +9725,42 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>$2,658</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>$3,535</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>$6,113</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>$4,564</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -9887,77 +9887,77 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
           <t>578</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>134</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>$2,610</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>$3,471</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>$6,002</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>$4,480</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>200</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -10049,17 +10049,17 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -10069,17 +10069,17 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>$2,589</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>$3,443</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>$5,954</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -10211,72 +10211,72 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
           <t>620</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>314</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>$2,808</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>$3,734</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>$6,458</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>$4,820</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>326</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -10373,42 +10373,42 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>$2,731</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>$3,632</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>$6,281</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>$4,689</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -10535,42 +10535,42 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>$2,669</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>$3,549</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>$6,138</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>$4,582</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -10697,77 +10697,77 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>$2,833</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>$3,767</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>$6,515</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>$4,863</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>608</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>314</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -10859,102 +10859,102 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
         <is>
           <t>$2,585</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="AD65" t="inlineStr">
         <is>
           <t>$3,438</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="AE65" t="inlineStr">
         <is>
           <t>$5,945</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>1345</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>1345</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>$2,585</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>$3,438</t>
-        </is>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>$5,945</t>
-        </is>
-      </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>$4,438</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -11021,102 +11021,102 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
         <is>
           <t>$3,345</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="AD66" t="inlineStr">
         <is>
           <t>$4,448</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="AE66" t="inlineStr">
         <is>
           <t>$7,693</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>$5,684</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>$3,345</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>$4,448</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>$7,693</t>
-        </is>
-      </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>$5,684</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -11183,77 +11183,77 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
           <t>578</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>134</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>$2,753</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>$3,661</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>$6,331</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>$4,726</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>1739</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>142</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -11345,102 +11345,102 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
           <t>1130</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>170</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
         <is>
           <t>$2,552</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="AD68" t="inlineStr">
         <is>
           <t>$3,394</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="AE68" t="inlineStr">
         <is>
           <t>$5,869</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>$2,552</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>$3,394</t>
-        </is>
-      </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>$5,869</t>
-        </is>
-      </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>$4,336</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -11507,77 +11507,77 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
           <t>578</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>314</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>134</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>$2,516</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>$3,346</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>$5,786</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>$4,318</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>1561</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>1096</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>170</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -11669,102 +11669,102 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>938</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
         <is>
           <t>$2,646</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="AD70" t="inlineStr">
         <is>
           <t>$3,519</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="AE70" t="inlineStr">
         <is>
           <t>$6,085</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>1490</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>1490</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>$2,646</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>$3,519</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>$6,085</t>
-        </is>
-      </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>$4,495</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -11831,42 +11831,42 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>$2,687</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>$3,573</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>$6,180</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>$4,612</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -11993,42 +11993,42 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>$2,781</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>$3,698</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>$6,396</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>$4,775</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -12155,102 +12155,102 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>1493</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>950</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>232</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
         <is>
           <t>$2,750</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="AD73" t="inlineStr">
         <is>
           <t>$3,657</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="AE73" t="inlineStr">
         <is>
           <t>$6,324</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>1493</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>1493</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>$2,750</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>$3,657</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>$6,324</t>
-        </is>
-      </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>$4,721</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -12317,42 +12317,42 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>$2,801</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>$3,725</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>$6,442</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>$4,759</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -12479,42 +12479,42 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>$2,514</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>$3,343</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>$5,782</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>$4,316</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -12641,42 +12641,42 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>$2,581</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>$3,432</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>$5,936</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>$4,431</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -12773,12 +12773,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>767-300ER (LAX-OSL 2), A380-800 (LASV-OSLO)</t>
+          <t>767-300ER (LAX-OSL 2), A330-800 (LAX-OSL 2), A380-800 (LASV-OSLO)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -12803,77 +12803,77 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>$2,455</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>$3,265</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>$4,445</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>$3,641</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>1551</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>1544</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
         <is>
           <t>472</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>192</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>1098</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>154</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -12965,77 +12965,77 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>132</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>$2,578</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>$3,428</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>$5,929</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>$4,425</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>156</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -13127,42 +13127,42 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>$2,815</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>$3,743</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>$6,474</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>$4,833</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -13289,42 +13289,42 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>$2,762</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>$3,673</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>$6,352</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>$4,741</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">

--- a/routes_output.xlsx
+++ b/routes_output.xlsx
@@ -633,17 +633,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>401</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>124</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -653,22 +653,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>76</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -688,22 +688,22 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>$4,795</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>401</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>346</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>114</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>686</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -850,22 +850,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>$4,002</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>346</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>114</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -957,17 +957,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>354</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>108</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -977,22 +977,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>66</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1012,22 +1012,22 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>$4,736</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>354</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>329</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>98</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1139,77 +1139,77 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>1710</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>$2,825</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>$3,757</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>$6,497</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>$4,800</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>323</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>323</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>268</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1463,77 +1463,77 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>$2,668</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>$3,548</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>$6,135</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1582</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>1434</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>$2,668</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>$3,548</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>$6,135</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>$4,620</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>1434</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1605,44 +1605,44 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1582</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1582</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>$2,170</t>
@@ -1665,17 +1665,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>400</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1767,97 +1767,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>$2,234</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>$2,971</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>$5,138</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1896</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>418</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>$2,234</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>$2,971</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>$5,138</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>$3,916</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1793</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1929,17 +1929,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>443</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>150</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1949,17 +1949,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>566</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>344</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>124</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1989,17 +1989,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>443</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>150</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -2091,17 +2091,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>444</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>580</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>340</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>122</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>444</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>150</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2253,17 +2253,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2273,57 +2273,57 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>$2,742</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>$3,647</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>$6,307</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>$4,750</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2415,17 +2415,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>275</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2475,17 +2475,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>262</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2577,17 +2577,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>413</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>131</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>413</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>131</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2739,97 +2739,97 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>$2,704</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>$3,596</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>$6,219</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>424</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>143</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2921,57 +2921,57 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>$1,981</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>$2,635</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>$4,556</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>424</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>143</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>426</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>144</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -3123,17 +3123,17 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>426</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -3225,17 +3225,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>248</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3245,57 +3245,57 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>1184</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>$2,609</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>$3,470</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>$6,001</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>367</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>121</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3407,57 +3407,57 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>$2,590</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>$3,444</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>$5,955</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>367</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>121</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>356</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3569,57 +3569,57 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>842</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>274</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,662</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,540</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,122</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,659</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>356</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>109</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -3711,17 +3711,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>159</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3731,57 +3731,57 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,633</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,502</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,055</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,560</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>159</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -3873,17 +3873,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>269</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3933,17 +3933,17 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>269</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -4035,17 +4035,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>331</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>98</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -4095,17 +4095,17 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>331</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>98</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -4197,17 +4197,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>299</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>92</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -4257,17 +4257,17 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>299</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>92</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -4359,17 +4359,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>317</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>96</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4379,57 +4379,57 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,718</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,614</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,251</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,758</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>317</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>96</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -4439,17 +4439,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -4521,17 +4521,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>315</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>98</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4541,57 +4541,57 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
+          <t>$2,415</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>$3,212</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>$5,553</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>315</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>98</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -4683,17 +4683,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>235</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>235</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -4763,42 +4763,42 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>902</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,624</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,489</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,035</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,653</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>404</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>132</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -4865,57 +4865,57 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>$2,723</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>$3,622</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>$6,262</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>404</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>132</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -5007,17 +5007,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>416</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -5027,57 +5027,57 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>790</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>284</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,706</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,598</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,223</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,580</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>416</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -5087,17 +5087,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>404</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>135</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>261</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -5189,57 +5189,57 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>902</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>172</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,506</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,332</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,763</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,448</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>261</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -5331,17 +5331,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>448</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>149</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -5351,57 +5351,57 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,483</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,302</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,710</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,353</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>448</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>149</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -5493,17 +5493,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>336</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>101</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -5513,57 +5513,57 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,598</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,455</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,975</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,396</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>336</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>101</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -5573,17 +5573,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>322</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -5655,17 +5655,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>428</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>143</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -5675,57 +5675,57 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>692</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>278</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,052</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,660</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,424</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,642</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>428</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>143</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -5817,17 +5817,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>421</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -5837,57 +5837,57 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>748</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>298</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,228</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,963</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,124</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,770</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>421</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -5897,17 +5897,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5979,17 +5979,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>240</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -5999,57 +5999,57 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>912</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,208</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,937</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,078</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,817</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>393</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -6201,17 +6201,17 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>393</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>130</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6293,27 +6293,27 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>767-300ER (KIX-IST 2), A380-800 (KIX-ISTANBUL)</t>
+          <t>767-300ER (KIX-IST 2), A350-900XWB (KIX-IST 3), A380-800 (KIX-ISTANBUL)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>488</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>171</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -6323,57 +6323,57 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>$2,553</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>$3,395</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>$5,871</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>488</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>171</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -6383,17 +6383,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>468</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -6465,17 +6465,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>284</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -6525,17 +6525,17 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>284</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -6545,24 +6545,24 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
           <t>$2,355</t>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,985</t>
         </is>
       </c>
     </row>
@@ -6627,17 +6627,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>527</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -6647,57 +6647,57 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>720</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,694</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,583</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,196</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,577</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>527</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -6789,17 +6789,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>287</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -6809,57 +6809,57 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>844</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>202</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,198</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,923</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,055</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,733</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -6951,17 +6951,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>338</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -6971,57 +6971,57 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>324</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,616</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,479</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,016</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,427</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>338</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -7031,17 +7031,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>324</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -7113,17 +7113,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>490</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>165</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -7133,57 +7133,57 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,219</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,881</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,800</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,939</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>490</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -7275,17 +7275,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>452</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>165</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -7295,57 +7295,57 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,707</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,600</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,226</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,805</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>452</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -7355,17 +7355,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>440</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -7437,17 +7437,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>431</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>142</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -7457,57 +7457,57 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,280</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,033</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,244</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,997</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>431</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>142</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -7599,17 +7599,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>516</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>191</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -7659,17 +7659,17 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>516</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -7761,17 +7761,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>295</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -7821,17 +7821,17 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>295</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -7923,17 +7923,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>355</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -7943,57 +7943,57 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>938</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,617</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,480</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,019</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,428</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>355</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>109</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -8003,17 +8003,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>344</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>531</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>197</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -8105,57 +8105,57 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,444</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,251</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,621</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,286</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>531</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -8247,17 +8247,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>287</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -8267,57 +8267,57 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
+          <t>$2,623</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>$3,488</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>$6,032</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -8409,17 +8409,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>318</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>87</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -8429,57 +8429,57 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>808</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>62</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,060</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,739</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,738</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,654</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>318</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>87</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -8489,17 +8489,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>300</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -8571,17 +8571,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>440</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>145</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -8591,57 +8591,57 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>648</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>296</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,206</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,021</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,225</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,859</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>440</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>257</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -8753,57 +8753,57 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
+          <t>$2,120</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>$2,819</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>$4,875</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -8813,22 +8813,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>224</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,671</t>
         </is>
       </c>
     </row>
@@ -8895,17 +8895,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>595</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>231</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -8955,17 +8955,17 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>595</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>231</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -8975,42 +8975,42 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,612</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,473</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,007</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,419</t>
         </is>
       </c>
     </row>
@@ -9057,17 +9057,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>512</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -9077,57 +9077,57 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
+          <t>$2,571</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>$3,419</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>$5,913</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>512</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>196</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -9137,22 +9137,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>480</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,367</t>
         </is>
       </c>
     </row>
@@ -9219,17 +9219,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>581</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>230</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -9239,57 +9239,57 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,741</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,645</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,303</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,748</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>581</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>230</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -9381,17 +9381,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>562</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>214</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -9441,17 +9441,17 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>562</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -9461,22 +9461,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>524</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>212</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,594</t>
         </is>
       </c>
     </row>
@@ -9543,17 +9543,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>543</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>212</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -9563,57 +9563,57 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>984</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>398</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>162</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,596</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,452</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,970</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,457</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>543</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>212</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -9705,17 +9705,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>428</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>147</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -9725,57 +9725,57 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>336</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,658</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,535</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,113</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,564</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>428</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -9867,17 +9867,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>663</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>271</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -9887,57 +9887,57 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,610</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,471</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,002</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,480</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>663</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>271</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -9947,17 +9947,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>906</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>466</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>200</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -10029,17 +10029,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>540</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>211</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -10089,17 +10089,17 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>540</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -10191,17 +10191,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>436</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>144</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -10211,57 +10211,57 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>620</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,808</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,734</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,458</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,820</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>436</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -10353,17 +10353,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>291</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -10373,57 +10373,57 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>958</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,731</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,632</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,281</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,689</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>291</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>97</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -10515,17 +10515,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>598</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>227</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -10535,57 +10535,57 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,669</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,549</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,138</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,582</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>598</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>227</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -10677,17 +10677,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>154</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -10697,57 +10697,57 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,833</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,767</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,515</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,863</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>453</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -10757,17 +10757,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>352</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -10839,17 +10839,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>509</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>199</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -10899,17 +10899,17 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>509</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -10919,22 +10919,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>476</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,438</t>
         </is>
       </c>
     </row>
@@ -11001,17 +11001,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>506</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>170</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -11061,17 +11061,17 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>506</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -11081,22 +11081,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>478</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>162</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,684</t>
         </is>
       </c>
     </row>
@@ -11163,17 +11163,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>492</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>178</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -11183,57 +11183,57 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,753</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,661</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,331</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,726</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>492</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -11243,17 +11243,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>354</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>142</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -11325,104 +11325,104 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>575</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>1548</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
           <t>$2,552</t>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,336</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>598</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>227</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -11507,57 +11507,57 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,516</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,346</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,786</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,318</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>598</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>227</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -11567,17 +11567,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>408</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -11649,17 +11649,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>472</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>177</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -11709,17 +11709,17 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>472</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -11729,22 +11729,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>442</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,495</t>
         </is>
       </c>
     </row>
@@ -11811,17 +11811,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>609</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>241</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -11831,57 +11831,57 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>578</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,687</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,573</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,180</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,612</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>609</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -11973,17 +11973,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>354</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>124</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -11993,57 +11993,57 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>800</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,781</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,698</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,396</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,775</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>354</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -12135,17 +12135,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>578</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>220</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -12155,57 +12155,57 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
+          <t>$2,750</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>$3,657</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>$6,324</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>578</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -12215,22 +12215,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>546</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>214</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,721</t>
         </is>
       </c>
     </row>
@@ -12297,17 +12297,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>542</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>211</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -12317,57 +12317,57 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q74" t="inlineStr">
         <is>
+          <t>$2,801</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>$3,725</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>$6,442</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>542</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -12459,17 +12459,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>560</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>207</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -12479,57 +12479,57 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q75" t="inlineStr">
         <is>
+          <t>$2,514</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>$3,343</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>$5,782</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>560</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>207</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -12621,17 +12621,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>435</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>166</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -12641,57 +12641,57 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>542</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>334</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,581</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,432</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,936</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,431</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>435</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>494</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>199</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -12803,57 +12803,57 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>424</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,455</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,265</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,445</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,641</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>494</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -12868,12 +12868,12 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -12945,17 +12945,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>441</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>161</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -12965,57 +12965,57 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>538</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>132</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,578</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,428</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5,929</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,425</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>441</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>161</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -13025,17 +13025,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -13107,17 +13107,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>529</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>206</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -13127,57 +13127,57 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>454</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$2,815</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$3,743</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$6,474</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4,833</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>529</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>206</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -13269,17 +13269,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>162</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -13289,57 +13289,57 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
+          <t>$2,762</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>$3,673</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>$6,352</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
           <t>$0</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>$0</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>453</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
